--- a/EasyCRM/10-Cost-Structure.xlsx
+++ b/EasyCRM/10-Cost-Structure.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A2:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -645,1867 +645,1694 @@
     <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>EASY
-CRM</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>COST STRUCTURE 2026</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" ht="24" customHeight="1"/>
     <row r="2" ht="20" customHeight="1">
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>โครงสร้างต้นทุน EasyCRM (บริษัท อีซี่สลิป จำกัด)</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>บันทึก</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>หมวด · รายการ</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>ผู้ให้บริการ</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>ลักษณะ · ความถี่</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>จำนวน × ราคา/หน่วย</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>ยอด (THB)</t>
+        </is>
+      </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>วันที่</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>ไตรมาส</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>หมวด</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>รายการ</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>ผู้ให้บริการ</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Fixed/Var</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>ความถี่</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>จำนวน</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>ราคา/หน่วย</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>ยอด/เดือน</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>ต้นทุนต่อเดือน แยกตามหมวด (THB)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>KPI ต้นทุน (THB)</t>
+      <c r="A4" s="14">
+        <f>IF(B4="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="14">
+        <f>IF(B4="","","Q"&amp;ROUNDUP(MONTH(B4)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>ค่าคอม</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>คอมเซลล์ Starter</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>ทีมขาย</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>ต่อดีล</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="17">
+        <f>IFERROR(I4*J4,0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>อ้างอิง Commission xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="18">
+        <f>IF(B5="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="18">
+        <f>IF(B5="","","Q"&amp;ROUNDUP(MONTH(B5)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>ค่าคอม</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>คอมเซลล์ Plus</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>ทีมขาย</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>ต่อดีล</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="21">
+        <f>IFERROR(I5*J5,0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="14">
+        <f>IF(B6="","","Q"&amp;ROUNDUP(MONTH(B6)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>ค่าคอม</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>คอมเซลล์ Premium</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>ทีมขาย</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>ต่อดีล</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17">
+        <f>IFERROR(I6*J6,0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18">
+        <f>IF(B7="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="18">
+        <f>IF(B7="","","Q"&amp;ROUNDUP(MONTH(B7)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>ค่าคอม</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>คอมเซลล์ Enterprise</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>ทีมขาย</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>ต่อดีล</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="21">
+        <f>IFERROR(I7*J7,0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14">
+        <f>IF(B8="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="14">
+        <f>IF(B8="","","Q"&amp;ROUNDUP(MONTH(B8)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>LINE API</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>EasySlip</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>รายได้/เดือน</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>ต้นทุน/เดือน</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <f>'ค่าคอมเซลล์'!E2</f>
-        <v/>
-      </c>
-      <c r="B6" s="6">
-        <f>LINE_API!E2</f>
-        <v/>
-      </c>
-      <c r="C6" s="6">
-        <f>EasySlip_Kbank!E2</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>Hosting!E2</f>
-        <v/>
-      </c>
-      <c r="E6" s="6">
-        <f>ทีม!E2</f>
-        <v/>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <f>E7</f>
-        <v/>
-      </c>
-      <c r="I6" s="7">
-        <f>G6-H6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>รวมต้นทุนทุกหมวด / เดือน</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="6">
-        <f>SUM(A6:E6)+อื่นๆ!E2</f>
-        <v/>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>จำนวนร้านค้า Active / Gross Margin %</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="10" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>รวมต้นทุน / ปี (×12)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="6">
-        <f>E7*12</f>
-        <v/>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <f>IF(G8=0,0,H6/G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="11">
-        <f>IF(G6=0,0,(G6-H6)/G6)</f>
-        <v/>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>LINE Push Message</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>LINE</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>ต่อข้อความ</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K8" s="17">
+        <f>IFERROR(I8*J8,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Premium ~0.15 บาท/msg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18">
+        <f>IF(B9="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="18">
+        <f>IF(B9="","","Q"&amp;ROUNDUP(MONTH(B9)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>LINE API</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>LINE Broadcast</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>LINE</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>ต่อข้อความ</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K9" s="21">
+        <f>IFERROR(I9*J9,0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14">
+        <f>IF(B10="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="14">
+        <f>IF(B10="","","Q"&amp;ROUNDUP(MONTH(B10)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>LINE API</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>LINE OA Premium plan</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>LINE</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K10" s="17">
+        <f>IFERROR(I10*J10,0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>เลือกแผนตามจริง</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>บันทึก</t>
-        </is>
+      <c r="A11" s="18">
+        <f>IF(B11="","",ROW()-3)</f>
+        <v/>
       </c>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="10" t="n"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>หมวด · รายการ</t>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>EasySlip</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>ผู้ให้บริการ</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>ลักษณะ · ความถี่</t>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>Kbank</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Variable</t>
         </is>
       </c>
       <c r="H11" s="10" t="n"/>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>จำนวน × ราคา/หน่วย</t>
-        </is>
+      <c r="I11" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="10" t="n"/>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>ยอด (THB)</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
+      <c r="K11" s="21">
+        <f>IFERROR(I11*J11,0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>ม.ค. 2569 อัตราคงที่ 0.04 บาท</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>วันที่</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>ไตรมาส</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>หมวด</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>รายการ</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>ผู้ให้บริการ</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>Fixed/Var</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>ความถี่</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>จำนวน</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>ราคา/หน่วย</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
-        <is>
-          <t>ยอด/เดือน</t>
-        </is>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
+      <c r="A12" s="14">
+        <f>IF(B12="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="14">
+        <f>IF(B12="","","Q"&amp;ROUNDUP(MONTH(B12)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>EasySlip</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>ต่างธนาคาร (Others)</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Kbank</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>ต่อสลิป</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K12" s="17">
+        <f>IFERROR(I12*J12,0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>อัตราคงที่ 0.11 บาท/สลิป</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14">
-        <f>IF(B13="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="14">
+      <c r="A13" s="18">
+        <f>IF(B13="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="18">
         <f>IF(B13="","","Q"&amp;ROUNDUP(MONTH(B13)/3,0))</f>
         <v/>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>ค่าคอม</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>คอมเซลล์ Starter</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>ทีมขาย</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>EasySlip</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>EasySlip API (in-house)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>EasySlip</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>ต่อดีล</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="17">
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>ต่อสลิป</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="21">
         <f>IFERROR(I13*J13,0)</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>อ้างอิง Commission xlsx</t>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>ใส่ต้นทุนภายในถ้ามี</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18">
-        <f>IF(B14="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="18">
+      <c r="A14" s="14">
+        <f>IF(B14="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="14">
         <f>IF(B14="","","Q"&amp;ROUNDUP(MONTH(B14)/3,0))</f>
         <v/>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>ค่าคอม</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>คอมเซลล์ Plus</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>ทีมขาย</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Frontend Hosting</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Vercel</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17">
+        <f>IFERROR(I14*J14,0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>easycrm-two.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18">
+        <f>IF(B15="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="18">
+        <f>IF(B15="","","Q"&amp;ROUNDUP(MONTH(B15)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>Supabase/Vercel</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="21">
+        <f>IFERROR(I15*J15,0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14">
+        <f>IF(B16="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="14">
+        <f>IF(B16="","","Q"&amp;ROUNDUP(MONTH(B16)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>Object Storage</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>S3/R2</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>ต่อดีล</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
-        <f>IFERROR(I14*J14,0)</f>
-        <v/>
-      </c>
-      <c r="L14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14">
-        <f>IF(B15="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="14">
-        <f>IF(B15="","","Q"&amp;ROUNDUP(MONTH(B15)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>ค่าคอม</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>คอมเซลล์ Premium</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>ทีมขาย</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <f>IFERROR(I16*J16,0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>รูปสลิป/ใบเสร็จ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18">
+        <f>IF(B17="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="18">
+        <f>IF(B17="","","Q"&amp;ROUNDUP(MONTH(B17)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Domain easy-crm.co</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>รายปี / 12</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="21">
+        <f>IFERROR(I17*J17,0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>ราคาทั้งปี ÷ 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14">
+        <f>IF(B18="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="14">
+        <f>IF(B18="","","Q"&amp;ROUNDUP(MONTH(B18)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Email Transactional</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Resend/SES</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>ต่อดีล</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <f>IFERROR(I15*J15,0)</f>
-        <v/>
-      </c>
-      <c r="L15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18">
-        <f>IF(B16="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="18">
-        <f>IF(B16="","","Q"&amp;ROUNDUP(MONTH(B16)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>ค่าคอม</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>คอมเซลล์ Enterprise</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>ทีมขาย</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="17">
+        <f>IFERROR(I18*J18,0)</f>
+        <v/>
+      </c>
+      <c r="L18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18">
+        <f>IF(B19="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="18">
+        <f>IF(B19="","","Q"&amp;ROUNDUP(MONTH(B19)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Hosting</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>Monitoring / Backup</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21">
+        <f>IFERROR(I19*J19,0)</f>
+        <v/>
+      </c>
+      <c r="L19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14">
+        <f>IF(B20="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="14">
+        <f>IF(B20="","","Q"&amp;ROUNDUP(MONTH(B20)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>ทีม</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Admin Support / Onboarding</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>ภายใน</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="17">
+        <f>IFERROR(I20*J20,0)</f>
+        <v/>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>เงินเดือน × จำนวนคน</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18">
+        <f>IF(B21="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="18">
+        <f>IF(B21="","","Q"&amp;ROUNDUP(MONTH(B21)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>ทีม</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>Designer</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>ภายใน</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="21">
+        <f>IFERROR(I21*J21,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14">
+        <f>IF(B22="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="14">
+        <f>IF(B22="","","Q"&amp;ROUNDUP(MONTH(B22)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>ทีม</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>Tech / Dev support</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>ภายใน</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="17">
+        <f>IFERROR(I22*J22,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18">
+        <f>IF(B23="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="18">
+        <f>IF(B23="","","Q"&amp;ROUNDUP(MONTH(B23)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>ทีม</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>PM / Product Owner</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>ภายใน</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="21">
+        <f>IFERROR(I23*J23,0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14">
+        <f>IF(B24="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="14">
+        <f>IF(B24="","","Q"&amp;ROUNDUP(MONTH(B24)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>ทีม</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>Sales (fixed)</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>ภายใน</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17">
+        <f>IFERROR(I24*J24,0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนค่าคอมมิชชันรวมอยู่หมวด ค่าคอม</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18">
+        <f>IF(B25="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="18">
+        <f>IF(B25="","","Q"&amp;ROUNDUP(MONTH(B25)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>อื่นๆ</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Marketing / Ads</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>หลายราย</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>ต่อดีล</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="21">
-        <f>IFERROR(I16*J16,0)</f>
-        <v/>
-      </c>
-      <c r="L16" s="20" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14">
-        <f>IF(B17="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="14">
-        <f>IF(B17="","","Q"&amp;ROUNDUP(MONTH(B17)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>LINE API</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>LINE Push Message</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>LINE</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="21">
+        <f>IFERROR(I25*J25,0)</f>
+        <v/>
+      </c>
+      <c r="L25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14">
+        <f>IF(B26="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="14">
+        <f>IF(B26="","","Q"&amp;ROUNDUP(MONTH(B26)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>อื่นๆ</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>Tools / SaaS</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Notion/Slack/etc</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="17">
+        <f>IFERROR(I26*J26,0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18">
+        <f>IF(B27="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="18">
+        <f>IF(B27="","","Q"&amp;ROUNDUP(MONTH(B27)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>อื่นๆ</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>Payment Gateway fee</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>Stripe/Omise</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>ต่อข้อความ</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K17" s="17">
-        <f>IFERROR(I17*J17,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>Premium ~0.15 บาท/msg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18">
-        <f>IF(B18="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="18">
-        <f>IF(B18="","","Q"&amp;ROUNDUP(MONTH(B18)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>LINE API</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>LINE Broadcast</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>LINE</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>% ของยอด</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="21">
+        <f>IFERROR(I27*J27,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>กรณีมี recurring billing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14">
+        <f>IF(B28="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="14">
+        <f>IF(B28="","","Q"&amp;ROUNDUP(MONTH(B28)/3,0))</f>
+        <v/>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>อื่นๆ</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>ค่าใช้จ่ายเบ็ดเตล็ด</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>ต่อข้อความ</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K18" s="21">
-        <f>IFERROR(I18*J18,0)</f>
-        <v/>
-      </c>
-      <c r="L18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14">
-        <f>IF(B19="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="14">
-        <f>IF(B19="","","Q"&amp;ROUNDUP(MONTH(B19)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>LINE API</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>LINE OA Premium plan</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>LINE</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>รายเดือน</t>
         </is>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I28" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="17" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K19" s="17">
-        <f>IFERROR(I19*J19,0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>เลือกแผนตามจริง</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18">
-        <f>IF(B20="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="18">
-        <f>IF(B20="","","Q"&amp;ROUNDUP(MONTH(B20)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>EasySlip</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>Kbank K2K (in-source)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>Kbank</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>ต่อสลิป</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="21" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K20" s="21">
-        <f>IFERROR(I20*J20,0)</f>
-        <v/>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>ม.ค. 2569 อัตราคงที่ 0.04 บาท</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14">
-        <f>IF(B21="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="14">
-        <f>IF(B21="","","Q"&amp;ROUNDUP(MONTH(B21)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>EasySlip</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>ต่างธนาคาร (Others)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>Kbank</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>ต่อสลิป</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K21" s="17">
-        <f>IFERROR(I21*J21,0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>อัตราคงที่ 0.11 บาท/สลิป</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18">
-        <f>IF(B22="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="18">
-        <f>IF(B22="","","Q"&amp;ROUNDUP(MONTH(B22)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>EasySlip</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>EasySlip API (in-house)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>EasySlip</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>ต่อสลิป</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="21">
-        <f>IFERROR(I22*J22,0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>ใส่ต้นทุนภายในถ้ามี</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14">
-        <f>IF(B23="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="14">
-        <f>IF(B23="","","Q"&amp;ROUNDUP(MONTH(B23)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>Frontend Hosting</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>Vercel</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="17">
-        <f>IFERROR(I23*J23,0)</f>
-        <v/>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>easycrm-two.vercel.app</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18">
-        <f>IF(B24="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="18">
-        <f>IF(B24="","","Q"&amp;ROUNDUP(MONTH(B24)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>Supabase/Vercel</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="21">
-        <f>IFERROR(I24*J24,0)</f>
-        <v/>
-      </c>
-      <c r="L24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14">
-        <f>IF(B25="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="14">
-        <f>IF(B25="","","Q"&amp;ROUNDUP(MONTH(B25)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>Object Storage</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>S3/R2</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="17">
-        <f>IFERROR(I25*J25,0)</f>
-        <v/>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>รูปสลิป/ใบเสร็จ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18">
-        <f>IF(B26="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="18">
-        <f>IF(B26="","","Q"&amp;ROUNDUP(MONTH(B26)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Domain easy-crm.co</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>Registrar</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>รายปี / 12</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="21">
-        <f>IFERROR(I26*J26,0)</f>
-        <v/>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>ราคาทั้งปี ÷ 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14">
-        <f>IF(B27="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="14">
-        <f>IF(B27="","","Q"&amp;ROUNDUP(MONTH(B27)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>Email Transactional</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>Resend/SES</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="17">
-        <f>IFERROR(I27*J27,0)</f>
-        <v/>
-      </c>
-      <c r="L27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18">
-        <f>IF(B28="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="18">
-        <f>IF(B28="","","Q"&amp;ROUNDUP(MONTH(B28)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>Hosting</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Monitoring / Backup</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="21">
+      <c r="J28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="17">
         <f>IFERROR(I28*J28,0)</f>
         <v/>
       </c>
-      <c r="L28" s="20" t="inlineStr"/>
+      <c r="L28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="14">
-        <f>IF(B29="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="14">
+      <c r="A29" s="18">
+        <f>IF(B29="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="18">
         <f>IF(B29="","","Q"&amp;ROUNDUP(MONTH(B29)/3,0))</f>
         <v/>
       </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>Admin Support / Onboarding</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>ภายใน</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="17">
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="21">
         <f>IFERROR(I29*J29,0)</f>
         <v/>
       </c>
-      <c r="L29" s="16" t="inlineStr">
-        <is>
-          <t>เงินเดือน × จำนวนคน</t>
-        </is>
-      </c>
+      <c r="L29" s="20" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18">
-        <f>IF(B30="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="18">
+      <c r="A30" s="14">
+        <f>IF(B30="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="14">
         <f>IF(B30="","","Q"&amp;ROUNDUP(MONTH(B30)/3,0))</f>
         <v/>
       </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>Designer</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>ภายใน</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="21">
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17">
         <f>IFERROR(I30*J30,0)</f>
         <v/>
       </c>
-      <c r="L30" s="20" t="inlineStr"/>
+      <c r="L30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="14">
-        <f>IF(B31="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="14">
+      <c r="A31" s="18">
+        <f>IF(B31="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="18">
         <f>IF(B31="","","Q"&amp;ROUNDUP(MONTH(B31)/3,0))</f>
         <v/>
       </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>Tech / Dev support</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>ภายใน</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="17">
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="21">
         <f>IFERROR(I31*J31,0)</f>
         <v/>
       </c>
-      <c r="L31" s="16" t="inlineStr"/>
+      <c r="L31" s="20" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18">
-        <f>IF(B32="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="18">
+      <c r="A32" s="14">
+        <f>IF(B32="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="14">
         <f>IF(B32="","","Q"&amp;ROUNDUP(MONTH(B32)/3,0))</f>
         <v/>
       </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>PM / Product Owner</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>ภายใน</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="21">
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17">
         <f>IFERROR(I32*J32,0)</f>
         <v/>
       </c>
-      <c r="L32" s="20" t="inlineStr"/>
+      <c r="L32" s="16" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="14">
-        <f>IF(B33="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="14">
+      <c r="A33" s="18">
+        <f>IF(B33="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="18">
         <f>IF(B33="","","Q"&amp;ROUNDUP(MONTH(B33)/3,0))</f>
         <v/>
       </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>Sales (fixed)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>ภายใน</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="17">
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="21" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="21">
         <f>IFERROR(I33*J33,0)</f>
         <v/>
       </c>
-      <c r="L33" s="16" t="inlineStr">
-        <is>
-          <t>ส่วนค่าคอมมิชชันรวมอยู่หมวด ค่าคอม</t>
-        </is>
-      </c>
+      <c r="L33" s="20" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18">
-        <f>IF(B34="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="18">
+      <c r="A34" s="14">
+        <f>IF(B34="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="14">
         <f>IF(B34="","","Q"&amp;ROUNDUP(MONTH(B34)/3,0))</f>
         <v/>
       </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>อื่นๆ</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>Marketing / Ads</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>หลายราย</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="21">
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="16" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17">
         <f>IFERROR(I34*J34,0)</f>
         <v/>
       </c>
-      <c r="L34" s="20" t="inlineStr"/>
+      <c r="L34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="14">
-        <f>IF(B35="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="14">
+      <c r="A35" s="18">
+        <f>IF(B35="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="18">
         <f>IF(B35="","","Q"&amp;ROUNDUP(MONTH(B35)/3,0))</f>
         <v/>
       </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>อื่นๆ</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>Tools / SaaS</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>Notion/Slack/etc</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="17">
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="21" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="21">
         <f>IFERROR(I35*J35,0)</f>
         <v/>
       </c>
-      <c r="L35" s="16" t="inlineStr"/>
+      <c r="L35" s="20" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18">
-        <f>IF(B36="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="18">
+      <c r="A36" s="14">
+        <f>IF(B36="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="14">
         <f>IF(B36="","","Q"&amp;ROUNDUP(MONTH(B36)/3,0))</f>
         <v/>
       </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>อื่นๆ</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>Payment Gateway fee</t>
-        </is>
-      </c>
-      <c r="F36" s="20" t="inlineStr">
-        <is>
-          <t>Stripe/Omise</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>% ของยอด</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="21">
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17">
         <f>IFERROR(I36*J36,0)</f>
         <v/>
       </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>กรณีมี recurring billing</t>
-        </is>
-      </c>
+      <c r="L36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="14">
-        <f>IF(B37="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="14">
+      <c r="A37" s="18">
+        <f>IF(B37="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="18">
         <f>IF(B37="","","Q"&amp;ROUNDUP(MONTH(B37)/3,0))</f>
         <v/>
       </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>อื่นๆ</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>ค่าใช้จ่ายเบ็ดเตล็ด</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>รายเดือน</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="17">
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="20" t="n"/>
+      <c r="I37" s="21" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="21">
         <f>IFERROR(I37*J37,0)</f>
         <v/>
       </c>
-      <c r="L37" s="16" t="inlineStr"/>
+      <c r="L37" s="20" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18">
-        <f>IF(B38="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="18">
+      <c r="A38" s="14">
+        <f>IF(B38="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="14">
         <f>IF(B38="","","Q"&amp;ROUNDUP(MONTH(B38)/3,0))</f>
         <v/>
       </c>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="20" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="20" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21">
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17">
         <f>IFERROR(I38*J38,0)</f>
         <v/>
       </c>
-      <c r="L38" s="20" t="n"/>
+      <c r="L38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="14">
-        <f>IF(B39="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="14">
+      <c r="A39" s="18">
+        <f>IF(B39="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="18">
         <f>IF(B39="","","Q"&amp;ROUNDUP(MONTH(B39)/3,0))</f>
         <v/>
       </c>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="17" t="n"/>
-      <c r="J39" s="17" t="n"/>
-      <c r="K39" s="17">
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="21" t="n"/>
+      <c r="J39" s="21" t="n"/>
+      <c r="K39" s="21">
         <f>IFERROR(I39*J39,0)</f>
         <v/>
       </c>
-      <c r="L39" s="16" t="n"/>
+      <c r="L39" s="20" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18">
-        <f>IF(B40="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="18">
+      <c r="A40" s="14">
+        <f>IF(B40="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="14">
         <f>IF(B40="","","Q"&amp;ROUNDUP(MONTH(B40)/3,0))</f>
         <v/>
       </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="20" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21" t="n"/>
-      <c r="K40" s="21">
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="16" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17">
         <f>IFERROR(I40*J40,0)</f>
         <v/>
       </c>
-      <c r="L40" s="20" t="n"/>
+      <c r="L40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="14">
-        <f>IF(B41="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="14">
+      <c r="A41" s="18">
+        <f>IF(B41="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="18">
         <f>IF(B41="","","Q"&amp;ROUNDUP(MONTH(B41)/3,0))</f>
         <v/>
       </c>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="14" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="17" t="n"/>
-      <c r="J41" s="17" t="n"/>
-      <c r="K41" s="17">
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="21" t="n"/>
+      <c r="J41" s="21" t="n"/>
+      <c r="K41" s="21">
         <f>IFERROR(I41*J41,0)</f>
         <v/>
       </c>
-      <c r="L41" s="16" t="n"/>
+      <c r="L41" s="20" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18">
-        <f>IF(B42="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="18">
+      <c r="A42" s="14">
+        <f>IF(B42="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="14">
         <f>IF(B42="","","Q"&amp;ROUNDUP(MONTH(B42)/3,0))</f>
         <v/>
       </c>
-      <c r="D42" s="20" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="20" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="20" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21" t="n"/>
-      <c r="K42" s="21">
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="16" t="n"/>
+      <c r="I42" s="17" t="n"/>
+      <c r="J42" s="17" t="n"/>
+      <c r="K42" s="17">
         <f>IFERROR(I42*J42,0)</f>
         <v/>
       </c>
-      <c r="L42" s="20" t="n"/>
+      <c r="L42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="14">
-        <f>IF(B43="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="14">
+      <c r="A43" s="18">
+        <f>IF(B43="","",ROW()-3)</f>
+        <v/>
+      </c>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="18">
         <f>IF(B43="","","Q"&amp;ROUNDUP(MONTH(B43)/3,0))</f>
         <v/>
       </c>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="16" t="n"/>
-      <c r="I43" s="17" t="n"/>
-      <c r="J43" s="17" t="n"/>
-      <c r="K43" s="17">
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="21" t="n"/>
+      <c r="J43" s="21" t="n"/>
+      <c r="K43" s="21">
         <f>IFERROR(I43*J43,0)</f>
         <v/>
       </c>
-      <c r="L43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="18">
-        <f>IF(B44="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="18">
-        <f>IF(B44="","","Q"&amp;ROUNDUP(MONTH(B44)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D44" s="20" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="20" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="20" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21">
-        <f>IFERROR(I44*J44,0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="20" t="n"/>
+      <c r="L43" s="20" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="14">
-        <f>IF(B45="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B45" s="15" t="n"/>
-      <c r="C45" s="14">
-        <f>IF(B45="","","Q"&amp;ROUNDUP(MONTH(B45)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="14" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="17" t="n"/>
-      <c r="J45" s="17" t="n"/>
-      <c r="K45" s="17">
-        <f>IFERROR(I45*J45,0)</f>
-        <v/>
-      </c>
-      <c r="L45" s="16" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="18">
-        <f>IF(B46="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="18">
-        <f>IF(B46="","","Q"&amp;ROUNDUP(MONTH(B46)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="18" t="n"/>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21">
-        <f>IFERROR(I46*J46,0)</f>
-        <v/>
-      </c>
-      <c r="L46" s="20" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="14">
-        <f>IF(B47="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="14">
-        <f>IF(B47="","","Q"&amp;ROUNDUP(MONTH(B47)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="14" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="17" t="n"/>
-      <c r="J47" s="17" t="n"/>
-      <c r="K47" s="17">
-        <f>IFERROR(I47*J47,0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="16" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="18">
-        <f>IF(B48="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="18">
-        <f>IF(B48="","","Q"&amp;ROUNDUP(MONTH(B48)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D48" s="20" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="20" t="n"/>
-      <c r="G48" s="18" t="n"/>
-      <c r="H48" s="20" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21">
-        <f>IFERROR(I48*J48,0)</f>
-        <v/>
-      </c>
-      <c r="L48" s="20" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="14">
-        <f>IF(B49="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="14">
-        <f>IF(B49="","","Q"&amp;ROUNDUP(MONTH(B49)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="17" t="n"/>
-      <c r="J49" s="17" t="n"/>
-      <c r="K49" s="17">
-        <f>IFERROR(I49*J49,0)</f>
-        <v/>
-      </c>
-      <c r="L49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="18">
-        <f>IF(B50="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="18">
-        <f>IF(B50="","","Q"&amp;ROUNDUP(MONTH(B50)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D50" s="20" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="20" t="n"/>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="20" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="J50" s="21" t="n"/>
-      <c r="K50" s="21">
-        <f>IFERROR(I50*J50,0)</f>
-        <v/>
-      </c>
-      <c r="L50" s="20" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="14">
-        <f>IF(B51="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="14">
-        <f>IF(B51="","","Q"&amp;ROUNDUP(MONTH(B51)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="17" t="n"/>
-      <c r="J51" s="17" t="n"/>
-      <c r="K51" s="17">
-        <f>IFERROR(I51*J51,0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18">
-        <f>IF(B52="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="18">
-        <f>IF(B52="","","Q"&amp;ROUNDUP(MONTH(B52)/3,0))</f>
-        <v/>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="18" t="n"/>
-      <c r="H52" s="20" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
-      <c r="K52" s="21">
-        <f>IFERROR(I52*J52,0)</f>
-        <v/>
-      </c>
-      <c r="L52" s="20" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>รวมต้นทุนจากตารางบันทึก / เดือน</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="22">
-        <f>SUM(K13:K52)</f>
-        <v/>
-      </c>
-      <c r="L54" s="23" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="22">
+        <f>SUM(K4:K43)</f>
+        <v/>
+      </c>
+      <c r="L45" s="23" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A8:D8"/>
+  <mergeCells count="5">
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="G4:I4"/>
     <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="G7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
